--- a/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
+++ b/docs/Mapping_casi_uso/trascrizioni/Trascr_Citt_999.xlsx
@@ -1723,7 +1723,7 @@
         <v>122</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>111</v>
